--- a/public/templates/Bom_Sample.xlsx
+++ b/public/templates/Bom_Sample.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
   <si>
     <t xml:space="preserve">Product Code</t>
   </si>
@@ -100,6 +100,15 @@
     <t xml:space="preserve">Consumption Qty</t>
   </si>
   <si>
+    <t xml:space="preserve">Consumption per unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pieces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Std Qty</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cost per unit</t>
   </si>
   <si>
@@ -113,6 +122,12 @@
   </si>
   <si>
     <t xml:space="preserve">Vendor Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remark</t>
   </si>
   <si>
     <t xml:space="preserve">Item code of the product for which BOM is to be defined</t>
@@ -142,43 +157,52 @@
     <t xml:space="preserve">Quantity in base UOM of RM required to product 1 unit of the Product</t>
   </si>
   <si>
+    <t xml:space="preserve">Norms, Enter only number</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cost of the RM. System will consider Cost price from item master if left blank. Ensure Cost price is defined in Item master</t>
   </si>
   <si>
     <t xml:space="preserve">Name of the Station defined in production Route.</t>
   </si>
   <si>
-    <t xml:space="preserve">FGTESTNLB001</t>
+    <t xml:space="preserve">This is item remark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FGTESTJ1I001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-house</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMTESTICI001</t>
   </si>
   <si>
     <t xml:space="preserve">Size</t>
   </si>
   <si>
-    <t xml:space="preserve">In-house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing Production Route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMTESTICI001</t>
-  </si>
-  <si>
     <t xml:space="preserve">STATION A</t>
   </si>
   <si>
-    <t xml:space="preserve">Color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRTESTWIM001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STATION B</t>
+    <t xml:space="preserve">This is project section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is project sub section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSHV001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sadasdas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etfsau</t>
   </si>
 </sst>
 </file>
@@ -383,7 +407,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.43"/>
@@ -410,12 +434,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="17.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="16.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="17.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="18.52"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1022" min="32" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="27" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="17.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="18.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="36" style="1" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -512,112 +537,138 @@
       <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>32</v>
+        <v>45</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -627,19 +678,19 @@
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="Q3" s="5" t="n">
         <v>1</v>
@@ -653,28 +704,43 @@
       <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5" t="n">
-        <v>1.32</v>
+        <v>10</v>
       </c>
       <c r="AA3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="5" t="n">
         <v>10.25</v>
       </c>
-      <c r="AB3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
+      <c r="AE3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ3" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>48</v>
-      </c>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -683,24 +749,12 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
@@ -709,18 +763,17 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="5"/>
-      <c r="Z4" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA4" s="5" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
@@ -754,6 +807,11 @@
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
       <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -787,6 +845,11 @@
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -820,6 +883,11 @@
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -853,6 +921,11 @@
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -886,6 +959,11 @@
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -919,6 +997,11 @@
       <c r="AC10" s="5"/>
       <c r="AD10" s="5"/>
       <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/public/templates/Bom_Sample.xlsx
+++ b/public/templates/Bom_Sample.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Consumption Qty</t>
   </si>
   <si>
-    <t xml:space="preserve">Consumption per unit</t>
+    <t xml:space="preserve">Component per unit</t>
   </si>
   <si>
     <t xml:space="preserve">Pieces</t>
@@ -439,7 +439,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="17.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="18.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="14.87"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="36" style="1" width="9.14"/>
   </cols>
   <sheetData>

--- a/public/templates/Bom_Sample.xlsx
+++ b/public/templates/Bom_Sample.xlsx
@@ -20,39 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t xml:space="preserve">Product Code</t>
   </si>
   <si>
-    <t xml:space="preserve">Product Attribute name 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute Value 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute name 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute Value 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute name 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute Value 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute name 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute Value 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute name 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Attribute Value 5</t>
+    <t xml:space="preserve">Product Attributes</t>
   </si>
   <si>
     <t xml:space="preserve">Production Type</t>
@@ -67,34 +40,7 @@
     <t xml:space="preserve">Item Code</t>
   </si>
   <si>
-    <t xml:space="preserve">Attribute name 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute Value 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute name 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute Value 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute name 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute Value 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute name 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute Value 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute name 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute Value 5</t>
+    <t xml:space="preserve">Item Attributes</t>
   </si>
   <si>
     <t xml:space="preserve">Consumption Qty</t>
@@ -133,7 +79,7 @@
     <t xml:space="preserve">Item code of the product for which BOM is to be defined</t>
   </si>
   <si>
-    <t xml:space="preserve">Leave blank if not applicable</t>
+    <t xml:space="preserve">If applicable should be in the specified format - Attribute Name:Attribute Value,  ….</t>
   </si>
   <si>
     <t xml:space="preserve">In-house 
@@ -166,10 +112,16 @@
     <t xml:space="preserve">Name of the Station defined in production Route.</t>
   </si>
   <si>
+    <t xml:space="preserve">Leave blank if not applicable</t>
+  </si>
+  <si>
     <t xml:space="preserve">This is item remark</t>
   </si>
   <si>
-    <t xml:space="preserve">FGTESTJ1I001</t>
+    <t xml:space="preserve">FGTESTIIO001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size:1,Color:red</t>
   </si>
   <si>
     <t xml:space="preserve">In-house</t>
@@ -181,10 +133,7 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">RMTESTICI001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
+    <t xml:space="preserve">RMTESTIIS001</t>
   </si>
   <si>
     <t xml:space="preserve">STATION A</t>
@@ -212,7 +161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -242,6 +191,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -305,7 +260,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -327,6 +282,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -407,40 +366,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="19.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="20.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="18.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="17.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="16.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="27" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="17.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="18.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="14.87"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="36" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1006" min="18" style="1" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -498,243 +441,117 @@
       <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
-        <v>48</v>
+        <v>30</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>10.25</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC3" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="AE3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ3" s="5" t="s">
-        <v>58</v>
+        <v>39</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -756,24 +573,6 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
@@ -794,24 +593,6 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="5"/>
-      <c r="AD5" s="5"/>
-      <c r="AE5" s="5"/>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5"/>
-      <c r="AJ5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -832,24 +613,6 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
-      <c r="AE6" s="5"/>
-      <c r="AF6" s="5"/>
-      <c r="AG6" s="5"/>
-      <c r="AH6" s="5"/>
-      <c r="AI6" s="5"/>
-      <c r="AJ6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -870,24 +633,6 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="5"/>
-      <c r="AD7" s="5"/>
-      <c r="AE7" s="5"/>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
-      <c r="AH7" s="5"/>
-      <c r="AI7" s="5"/>
-      <c r="AJ7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -908,24 +653,6 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="5"/>
-      <c r="AE8" s="5"/>
-      <c r="AF8" s="5"/>
-      <c r="AG8" s="5"/>
-      <c r="AH8" s="5"/>
-      <c r="AI8" s="5"/>
-      <c r="AJ8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -946,24 +673,6 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="5"/>
-      <c r="AD9" s="5"/>
-      <c r="AE9" s="5"/>
-      <c r="AF9" s="5"/>
-      <c r="AG9" s="5"/>
-      <c r="AH9" s="5"/>
-      <c r="AI9" s="5"/>
-      <c r="AJ9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -984,24 +693,6 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-      <c r="AH10" s="5"/>
-      <c r="AI10" s="5"/>
-      <c r="AJ10" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
